--- a/Sebake/CLIENT_HANDOVER_SPREADSHEET.xlsx
+++ b/Sebake/CLIENT_HANDOVER_SPREADSHEET.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Matsi\Desktop\gitMILA1\Sebake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9544EC54-B6DB-4859-BC7C-BD1A8E32D4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25067414-6653-494C-8132-4F63281E937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="109">
   <si>
     <t>Client Name</t>
   </si>
@@ -357,6 +357,12 @@
   </si>
   <si>
     <t>Client still negotiating so some fields can't be fill in yet</t>
+  </si>
+  <si>
+    <t>Dr Hlungwani</t>
+  </si>
+  <si>
+    <t>This guy wants a credit facility but needs to sit down with Mr. Myataza first so they can discuss percentages and how much you are willing to give him</t>
   </si>
 </sst>
 </file>
@@ -431,19 +437,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -729,7 +733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35" bestFit="1" customWidth="1"/>
@@ -797,48 +801,48 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>896930</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>200000</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <f>F2/D2</f>
         <v>0.245</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="7">
         <v>49000</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <f>D2+F2+$P$2</f>
         <v>251750</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2">
         <v>30</v>
       </c>
-      <c r="I2" s="5" t="s">
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="8">
         <v>725546809</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="M2" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="N2" t="s">
         <v>19</v>
       </c>
       <c r="P2">
@@ -846,370 +850,370 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>60564570.159999996</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>3500000</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <f t="shared" ref="E3:E8" si="0">F3/D3</f>
         <v>0.4</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>1400000</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <f t="shared" ref="G3:G8" si="1">D3+F3+$P$2</f>
         <v>4902750</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3">
         <v>120</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="8">
         <v>844405465</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" t="s">
         <v>45</v>
       </c>
-      <c r="N3" s="5" t="s">
+      <c r="N3" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>57339</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>43616.43</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <f t="shared" si="0"/>
         <v>0.15500007680591923</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>6760.55</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <f t="shared" si="1"/>
         <v>53126.98</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4">
         <v>30</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="8">
         <v>673219623</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" t="s">
         <v>31</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>722080</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>100000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <f t="shared" si="0"/>
         <v>0.3</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>30000</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <f t="shared" si="1"/>
         <v>132750</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5">
         <v>30</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" t="s">
         <v>37</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5" s="8">
         <v>813929698</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>11270000</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>11000000</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F6" s="3"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11">
+      <c r="G6" s="10"/>
+      <c r="H6">
         <v>30</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6" s="8">
         <v>731398794</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="5" t="s">
+      <c r="M6" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="5" t="s">
+      <c r="N6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <v>182600</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>112642.5</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <f t="shared" si="0"/>
         <v>0.15000004438821937</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>16896.38</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <f t="shared" si="1"/>
         <v>132288.88</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7">
         <v>30</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7" s="8">
         <v>721969359</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="5" t="s">
+      <c r="M7" t="s">
         <v>53</v>
       </c>
-      <c r="N7" s="5" t="s">
+      <c r="N7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>57599787.799999997</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>4000000</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <f t="shared" si="0"/>
         <v>0.4</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>1600000</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <f t="shared" si="1"/>
         <v>5602750</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8">
         <v>60</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" t="s">
         <v>58</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <v>793461241</v>
       </c>
-      <c r="L8" s="10" t="s">
+      <c r="L8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="5" t="s">
+      <c r="M8" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="5" t="s">
+      <c r="N8" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>62</v>
       </c>
       <c r="C9" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>5000000</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11">
+      <c r="G9" s="10"/>
+      <c r="H9">
         <v>60</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="8">
         <v>838864259</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="M9" s="5" t="s">
+      <c r="M9" t="s">
         <v>66</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N9" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>17000000</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="5" t="s">
+      <c r="G11" s="10"/>
+      <c r="H11" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" t="s">
         <v>42</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="8">
         <v>662224511</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M11" s="5" t="s">
+      <c r="M11" t="s">
         <v>44</v>
       </c>
-      <c r="N11" s="5" t="s">
+      <c r="N11" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1217,7 +1221,7 @@
       <c r="A12" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" t="s">
         <v>76</v>
       </c>
       <c r="C12" t="s">
@@ -1232,22 +1236,22 @@
       <c r="H12" t="s">
         <v>78</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" t="s">
         <v>14</v>
       </c>
       <c r="J12" t="s">
         <v>80</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="8">
         <v>766782343</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="M12" s="5" t="s">
+      <c r="M12" t="s">
         <v>81</v>
       </c>
-      <c r="N12" s="5" t="s">
+      <c r="N12" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1255,45 +1259,45 @@
       <c r="A13" t="s">
         <v>83</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>935400</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>400000</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <f t="shared" ref="E13:E17" si="2">F13/D13</f>
         <v>0.23499999999999999</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>94000</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <f t="shared" ref="G13:G17" si="3">D13+F13+$P$2</f>
         <v>496750</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13">
         <v>30</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" t="s">
         <v>14</v>
       </c>
       <c r="J13" t="s">
         <v>84</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <v>787523568</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M13" s="5" t="s">
+      <c r="M13" t="s">
         <v>86</v>
       </c>
-      <c r="N13" s="5" t="s">
+      <c r="N13" t="s">
         <v>87</v>
       </c>
     </row>
@@ -1301,42 +1305,42 @@
       <c r="A14" t="s">
         <v>88</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="5">
         <v>4000000</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>1000000</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <f t="shared" si="2"/>
         <v>0.3</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="5">
         <v>300000</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <f t="shared" si="3"/>
         <v>1302750</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14">
         <v>60</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" t="s">
         <v>14</v>
       </c>
       <c r="J14" t="s">
         <v>90</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <v>793963720</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="5" t="s">
+      <c r="M14" t="s">
         <v>92</v>
       </c>
       <c r="N14" t="s">
@@ -1347,45 +1351,45 @@
       <c r="A15" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="5">
         <v>1095000</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>500000</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <f t="shared" si="2"/>
         <v>0.28499999999999998</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="5">
         <v>142500</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <f t="shared" si="3"/>
         <v>645250</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15">
         <v>30</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" t="s">
         <v>14</v>
       </c>
       <c r="J15" t="s">
         <v>95</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <v>820788221</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="M15" s="5" t="s">
+      <c r="M15" t="s">
         <v>97</v>
       </c>
-      <c r="N15" s="5" t="s">
+      <c r="N15" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1393,45 +1397,45 @@
       <c r="A16" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <v>687500</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>442750</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <f t="shared" si="2"/>
         <v>0.185</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>81908.75</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <f t="shared" si="3"/>
         <v>527408.75</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16">
         <v>60</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" t="s">
         <v>14</v>
       </c>
       <c r="J16" t="s">
         <v>101</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>814189973</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="M16" s="5" t="s">
+      <c r="M16" t="s">
         <v>103</v>
       </c>
-      <c r="N16" s="5" t="s">
+      <c r="N16" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1442,16 +1446,16 @@
       <c r="B17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="10">
         <v>4766831.72</v>
       </c>
       <c r="D17" s="4"/>
-      <c r="E17" s="15" t="e">
+      <c r="E17" s="13" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F17" s="4"/>
-      <c r="G17" s="12">
+      <c r="G17" s="10">
         <f t="shared" si="3"/>
         <v>2750</v>
       </c>
@@ -1464,6 +1468,28 @@
         <v>106</v>
       </c>
       <c r="N17" s="4"/>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="3">
+        <v>762011450</v>
+      </c>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="N18" s="4"/>
     </row>
   </sheetData>
   <hyperlinks>
